--- a/references/Financial Estimation.xlsx
+++ b/references/Financial Estimation.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Ghiffary\Kerja\peereep\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\ghiffaryr\peereep-material\references\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FFEFB202-8940-4B4A-8063-B86B5E428FCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C96EBD0B-34C0-4BCC-94FE-7728DA646D24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="2" xr2:uid="{509BC320-9F37-49D3-AB39-00191F517526}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="1" xr2:uid="{509BC320-9F37-49D3-AB39-00191F517526}"/>
   </bookViews>
   <sheets>
     <sheet name="Opex" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="42">
   <si>
     <t>AWS DB</t>
   </si>
@@ -149,6 +149,24 @@
   </si>
   <si>
     <t>Amount per Unit ($)</t>
+  </si>
+  <si>
+    <t>Wallet</t>
+  </si>
+  <si>
+    <t>3 Cards Tangem Wallets</t>
+  </si>
+  <si>
+    <t>Bundle</t>
+  </si>
+  <si>
+    <t>Trezor Safe 3</t>
+  </si>
+  <si>
+    <t>Mainnet deployment</t>
+  </si>
+  <si>
+    <t>Security audit</t>
   </si>
 </sst>
 </file>
@@ -620,7 +638,8 @@
         <v>7.000000000000001E-4</v>
       </c>
       <c r="D4">
-        <v>8000</v>
+        <f>SUM(Revenue!D2:D5)</f>
+        <v>180000</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -633,7 +652,7 @@
       </c>
       <c r="H4">
         <f t="shared" si="0"/>
-        <v>5.6000000000000005</v>
+        <v>126.00000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
@@ -815,7 +834,7 @@
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="H12">
         <f>SUM(H2:H11)</f>
-        <v>57657.266666666656</v>
+        <v>57777.666666666657</v>
       </c>
     </row>
   </sheetData>
@@ -825,7 +844,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43BEDFFD-A6A2-4321-9290-A51FABB4BE55}">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="18.26953125" bestFit="1" customWidth="1"/>
@@ -868,6 +887,9 @@
       <c r="D2">
         <v>1000</v>
       </c>
+      <c r="E2" t="s">
+        <v>15</v>
+      </c>
       <c r="F2">
         <v>1</v>
       </c>
@@ -931,9 +953,111 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5">
+        <v>81.36</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5" t="s">
+        <v>27</v>
+      </c>
       <c r="H5">
-        <f>SUM(H2:H4)</f>
-        <v>803</v>
+        <f t="shared" ref="H5:H8" si="0">C5*D5</f>
+        <v>81.36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6">
+        <v>68.680000000000007</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6" t="s">
+        <v>3</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6">
+        <f t="shared" si="0"/>
+        <v>68.680000000000007</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7">
+        <v>172</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7" t="s">
+        <v>3</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H7">
+        <f t="shared" si="0"/>
+        <v>172</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8">
+        <v>20000</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8" t="s">
+        <v>27</v>
+      </c>
+      <c r="H8">
+        <f t="shared" si="0"/>
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H9">
+        <f>SUM(H2:H8)</f>
+        <v>21125.040000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1025,7 +1149,7 @@
         <v>30</v>
       </c>
       <c r="H3">
-        <f t="shared" ref="H3:H5" si="0">C3*D3*F3</f>
+        <f t="shared" ref="H3:H4" si="0">C3*D3*F3</f>
         <v>20000</v>
       </c>
     </row>

--- a/references/Financial Estimation.xlsx
+++ b/references/Financial Estimation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\ghiffaryr\peereep-material\references\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05AFD171-0031-49AA-8DA0-BEDE2BFE96B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E31D101D-8B56-4116-910A-A232B3B215E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="13770" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="212">
   <si>
     <t>Year 1 Financial Summary</t>
   </si>
@@ -626,27 +626,18 @@
     <t>4-year, 1-year cliff</t>
   </si>
   <si>
-    <t>Built entire MVP, paid all costs, vision owner</t>
-  </si>
-  <si>
     <t>Renard Elyon Imawanto</t>
   </si>
   <si>
     <t>Lead Blockchain Engineer</t>
   </si>
   <si>
-    <t>Gasless tx, fee optimization, smart contract</t>
-  </si>
-  <si>
     <t>Linh</t>
   </si>
   <si>
     <t>COO</t>
   </si>
   <si>
-    <t>Product maturation, QA, operations</t>
-  </si>
-  <si>
     <t>Employee Pool</t>
   </si>
   <si>
@@ -656,9 +647,6 @@
     <t>As granted</t>
   </si>
   <si>
-    <t>Reserved for CTO, Marketing Lead, etc.</t>
-  </si>
-  <si>
     <t>Investors</t>
   </si>
   <si>
@@ -669,6 +657,24 @@
   </si>
   <si>
     <t>$500K at $3M post-money valuation</t>
+  </si>
+  <si>
+    <t>CTO</t>
+  </si>
+  <si>
+    <t>Built entire MVP, paid all costs, vision owner, investor relations. Highest equity reflects foundational sweat equity and financial risk taken.</t>
+  </si>
+  <si>
+    <t>Gasless tx, fee optimization, smart contract security hardening,  AWS scaling. Early co-founder contribution.</t>
+  </si>
+  <si>
+    <t>Product maturation, QA, operations. Identified critical bugs during MVP phase to ensure product readiness and representative of CEO when needed.</t>
+  </si>
+  <si>
+    <t>Technical leadership, ensuring smart contract security, future AI integration plan, and investor relations.</t>
+  </si>
+  <si>
+    <t>Reserved for Marketing Lead, upcoming engineers, etc.</t>
   </si>
 </sst>
 </file>
@@ -2727,7 +2733,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="25" customWidth="1"/>
@@ -2763,27 +2769,27 @@
         <v>193</v>
       </c>
       <c r="C2" s="6">
-        <v>0.78</v>
+        <v>0.6</v>
       </c>
       <c r="D2" s="6">
-        <v>0.65</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="E2" t="s">
         <v>194</v>
       </c>
       <c r="F2" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>195</v>
+      </c>
+      <c r="B3" t="s">
         <v>196</v>
       </c>
-      <c r="B3" t="s">
-        <v>197</v>
-      </c>
       <c r="C3" s="6">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="D3" s="6">
         <v>7.4999999999999997E-2</v>
@@ -2792,77 +2798,96 @@
         <v>194</v>
       </c>
       <c r="F3" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B4" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C4" s="6">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="D4" s="6">
-        <v>6.7000000000000004E-2</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="E4" t="s">
         <v>194</v>
       </c>
       <c r="F4" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>202</v>
-      </c>
       <c r="B5" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C5" s="6">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
       <c r="D5" s="6">
-        <v>4.2000000000000003E-2</v>
+        <v>0.1</v>
       </c>
       <c r="E5" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="F5" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="B6" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="C6" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="D6" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="E6" t="s">
+        <v>201</v>
+      </c>
+      <c r="F6" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>202</v>
+      </c>
+      <c r="B7" t="s">
+        <v>203</v>
+      </c>
+      <c r="C7" s="6">
         <v>0</v>
       </c>
-      <c r="D6" s="6">
-        <v>0.16700000000000001</v>
-      </c>
-      <c r="E6" t="s">
-        <v>208</v>
-      </c>
-      <c r="F6" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="4" t="s">
+      <c r="D7" s="6">
+        <v>0.15</v>
+      </c>
+      <c r="E7" t="s">
+        <v>204</v>
+      </c>
+      <c r="F7" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C8" s="6">
+        <f>SUM(C2:C7)</f>
         <v>1</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D8" s="6">
+        <f>SUM(D2:D7)</f>
         <v>1</v>
       </c>
     </row>

--- a/references/Financial Estimation.xlsx
+++ b/references/Financial Estimation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\ghiffaryr\peereep-material\references\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{116AC706-7B6E-4567-AAB0-31C7CDE3C392}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{333E2366-CF1D-4360-B1D6-20CC2D46417F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,6 +41,519 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="197">
   <si>
+    <t>Year 1 Financial Summary</t>
+  </si>
+  <si>
+    <t>Profit &amp; Loss</t>
+  </si>
+  <si>
+    <t>Revenue</t>
+  </si>
+  <si>
+    <t>From Revenue sheet</t>
+  </si>
+  <si>
+    <t>Operating Expenses</t>
+  </si>
+  <si>
+    <t>From Opex sheet (post-funding)</t>
+  </si>
+  <si>
+    <t>Capital Expenses</t>
+  </si>
+  <si>
+    <t>From Capex sheet</t>
+  </si>
+  <si>
+    <t>Total Expenses</t>
+  </si>
+  <si>
+    <t>Profit</t>
+  </si>
+  <si>
+    <t>Profit Margin</t>
+  </si>
+  <si>
+    <t>GMV</t>
+  </si>
+  <si>
+    <t>Annual GMV = Total Trx x Avg Value x 12mo</t>
+  </si>
+  <si>
+    <t>Monthly GMV</t>
+  </si>
+  <si>
+    <t>Monthly GMV = Total Trx x Avg Value</t>
+  </si>
+  <si>
+    <t>Key Metrics</t>
+  </si>
+  <si>
+    <t>Monthly Burn (pre-funding)</t>
+  </si>
+  <si>
+    <t>Infrastructure only</t>
+  </si>
+  <si>
+    <t>Monthly Burn (post-funding)</t>
+  </si>
+  <si>
+    <t>Full team</t>
+  </si>
+  <si>
+    <t>Runway with $500K</t>
+  </si>
+  <si>
+    <t>$500K / monthly burn</t>
+  </si>
+  <si>
+    <t>Break-even</t>
+  </si>
+  <si>
+    <t>Month 1</t>
+  </si>
+  <si>
+    <t>Profitable from Day 1</t>
+  </si>
+  <si>
+    <t>Team Structure</t>
+  </si>
+  <si>
+    <t>Pre-Funding (3 founders)</t>
+  </si>
+  <si>
+    <t>Unpaid</t>
+  </si>
+  <si>
+    <t>Month 0 to funding</t>
+  </si>
+  <si>
+    <t>Post-Funding (6 people)</t>
+  </si>
+  <si>
+    <t>$69,749/month</t>
+  </si>
+  <si>
+    <t>$69,749/month - CEO, COO, CTO, Blockchain, Marketing, Content (incl. iOS fee)</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Base Users</t>
+  </si>
+  <si>
+    <t>Capture Rate</t>
+  </si>
+  <si>
+    <t>Active Users</t>
+  </si>
+  <si>
+    <t>Trx/Month per User</t>
+  </si>
+  <si>
+    <t>Total Trx/Month</t>
+  </si>
+  <si>
+    <t>Avg Trx Value ($)</t>
+  </si>
+  <si>
+    <t>Fee (%)</t>
+  </si>
+  <si>
+    <t>Fee per Trx ($)</t>
+  </si>
+  <si>
+    <t>Monthly Revenue ($)</t>
+  </si>
+  <si>
+    <t>Annual Revenue ($)</t>
+  </si>
+  <si>
+    <t>Reference</t>
+  </si>
+  <si>
+    <t>Monthly GMV ($)</t>
+  </si>
+  <si>
+    <t>Annual GMV ($)</t>
+  </si>
+  <si>
+    <t>Year 1 (1% Capture)</t>
+  </si>
+  <si>
+    <t>Tasks</t>
+  </si>
+  <si>
+    <t>Upwork 832K active clients × 1% capture × 0.2 trx/mo × $100 avg = $1.99M/yr GMV</t>
+  </si>
+  <si>
+    <t>Services</t>
+  </si>
+  <si>
+    <t>Goods</t>
+  </si>
+  <si>
+    <t>eBay 134M active buyers × 0.1% capture × 1.2 trx/mo × $50 avg = $96.48M/yr GMV</t>
+  </si>
+  <si>
+    <t>Secret Society</t>
+  </si>
+  <si>
+    <t>832 subs × $10/mo × 12mo = $99.8K/yr</t>
+  </si>
+  <si>
+    <t>Year 1 Total</t>
+  </si>
+  <si>
+    <t>Item</t>
+  </si>
+  <si>
+    <t>Cost per Unit ($)</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t>Frequency</t>
+  </si>
+  <si>
+    <t>Monthly Total ($)</t>
+  </si>
+  <si>
+    <t>Annual Total ($)</t>
+  </si>
+  <si>
+    <t>PRE-FUNDING (Month 0 to Funding)</t>
+  </si>
+  <si>
+    <t>Infrastructure</t>
+  </si>
+  <si>
+    <t>AWS ECR</t>
+  </si>
+  <si>
+    <t>User</t>
+  </si>
+  <si>
+    <t>Month</t>
+  </si>
+  <si>
+    <t>AWS pricing: $0.0035/user/mo</t>
+  </si>
+  <si>
+    <t>AWS DB</t>
+  </si>
+  <si>
+    <t>AWS pricing: $0.0015/user/mo</t>
+  </si>
+  <si>
+    <t>Blockchain</t>
+  </si>
+  <si>
+    <t>Network fee</t>
+  </si>
+  <si>
+    <t>Trx</t>
+  </si>
+  <si>
+    <t>Solana tx fee x 70 safety margin</t>
+  </si>
+  <si>
+    <t>Wallet fund</t>
+  </si>
+  <si>
+    <t>SOL for wallet operations</t>
+  </si>
+  <si>
+    <t>Pre-Funding Total</t>
+  </si>
+  <si>
+    <t>POST-FUNDING (Year 1)</t>
+  </si>
+  <si>
+    <t>Salary</t>
+  </si>
+  <si>
+    <t>CEO (Ghiffary)</t>
+  </si>
+  <si>
+    <t>Person</t>
+  </si>
+  <si>
+    <t>Founder salary</t>
+  </si>
+  <si>
+    <t>COO (Linh)</t>
+  </si>
+  <si>
+    <t>Operations + QA</t>
+  </si>
+  <si>
+    <t>CTO (To Hire)</t>
+  </si>
+  <si>
+    <t>Technical leadership</t>
+  </si>
+  <si>
+    <t>Lead Blockchain (Renard)</t>
+  </si>
+  <si>
+    <t>Smart contract + AWS</t>
+  </si>
+  <si>
+    <t>Senior Marketing Lead</t>
+  </si>
+  <si>
+    <t>Brand + Growth combined</t>
+  </si>
+  <si>
+    <t>Freelance Content Creator</t>
+  </si>
+  <si>
+    <t>Under Marketing Lead control</t>
+  </si>
+  <si>
+    <t>Office</t>
+  </si>
+  <si>
+    <t>Contact person</t>
+  </si>
+  <si>
+    <t>Company</t>
+  </si>
+  <si>
+    <t>Estonia e-residency</t>
+  </si>
+  <si>
+    <t>Rent exemption</t>
+  </si>
+  <si>
+    <t>Solana rent per account</t>
+  </si>
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>iOS App Store fee</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>Annual</t>
+  </si>
+  <si>
+    <t>Apple Developer Program (business account)</t>
+  </si>
+  <si>
+    <t>Post-Funding Total</t>
+  </si>
+  <si>
+    <t>Total ($)</t>
+  </si>
+  <si>
+    <t>E-residency</t>
+  </si>
+  <si>
+    <t>Estonia e-residency program</t>
+  </si>
+  <si>
+    <t>Company registration</t>
+  </si>
+  <si>
+    <t>Estonia business registration</t>
+  </si>
+  <si>
+    <t>Wallet</t>
+  </si>
+  <si>
+    <t>Tangem Wallets (3 cards)</t>
+  </si>
+  <si>
+    <t>Bundle</t>
+  </si>
+  <si>
+    <t>Tangem official pricing</t>
+  </si>
+  <si>
+    <t>Trezor Safe 3</t>
+  </si>
+  <si>
+    <t>Trezor official pricing</t>
+  </si>
+  <si>
+    <t>Mainnet deployment</t>
+  </si>
+  <si>
+    <t>Solana program deployment cost</t>
+  </si>
+  <si>
+    <t>Security audit</t>
+  </si>
+  <si>
+    <t>Solana/Anchor audit market rate</t>
+  </si>
+  <si>
+    <t>Total Capex</t>
+  </si>
+  <si>
+    <t>Phase</t>
+  </si>
+  <si>
+    <t>Timeline</t>
+  </si>
+  <si>
+    <t>Target Audience</t>
+  </si>
+  <si>
+    <t>Channels</t>
+  </si>
+  <si>
+    <t>DAU Target</t>
+  </si>
+  <si>
+    <t>GMV Target ($)</t>
+  </si>
+  <si>
+    <t>CAC Budget ($)</t>
+  </si>
+  <si>
+    <t>Users Target</t>
+  </si>
+  <si>
+    <t>CAC per User ($)</t>
+  </si>
+  <si>
+    <t>Phase 1: Proof of Concept</t>
+  </si>
+  <si>
+    <t>Months 1-3</t>
+  </si>
+  <si>
+    <t>Crypto-native</t>
+  </si>
+  <si>
+    <t>Solana ecosystem, Galxe quests, GitHub bounties</t>
+  </si>
+  <si>
+    <t>$6K seed campaign budget. Marketing salaries in runway.</t>
+  </si>
+  <si>
+    <t>Solana devs, designers, auditors</t>
+  </si>
+  <si>
+    <t>Phase 2: Regional Expansion</t>
+  </si>
+  <si>
+    <t>Months 4-9</t>
+  </si>
+  <si>
+    <t>Emerging markets</t>
+  </si>
+  <si>
+    <t>USDC referral rewards, Superteam collabs, translation</t>
+  </si>
+  <si>
+    <t>$12K seed campaign budget. $17.5K/mo team in runway.</t>
+  </si>
+  <si>
+    <t>1.4B unbanked workers in SEA, LATAM, Africa</t>
+  </si>
+  <si>
+    <t>Phase 3: Mainstream</t>
+  </si>
+  <si>
+    <t>Months 10+</t>
+  </si>
+  <si>
+    <t>Mainstream</t>
+  </si>
+  <si>
+    <t>Content marketing, crypto PR, organic marketplace velocity</t>
+  </si>
+  <si>
+    <t>$7K seed campaign. $100M GMV driven by organic + fee advantage.</t>
+  </si>
+  <si>
+    <t>Fee-fatigued professionals + eBay goods sellers</t>
+  </si>
+  <si>
+    <t>YEAR 1 TOTAL</t>
+  </si>
+  <si>
+    <t>GTM campaign budgets only; $105K marketing team in Opex runway</t>
+  </si>
+  <si>
+    <t>Budget ($)</t>
+  </si>
+  <si>
+    <t>Breakdown</t>
+  </si>
+  <si>
+    <t>OPERATIONAL RUNWAY (6 months)</t>
+  </si>
+  <si>
+    <t>6 months post-funding Opex</t>
+  </si>
+  <si>
+    <t>ONE-TIME SETUP</t>
+  </si>
+  <si>
+    <t>Capex (from Capex sheet)</t>
+  </si>
+  <si>
+    <t>E-residency, wallets, mainnet, security audit</t>
+  </si>
+  <si>
+    <t>INFRASTRUCTURE SCALING</t>
+  </si>
+  <si>
+    <t>AWS scaling buffer</t>
+  </si>
+  <si>
+    <t>Scale 8K to 50K users w/ 6x safety margin</t>
+  </si>
+  <si>
+    <t>Target $250/mo − Current $42/mo x 12mo x 6</t>
+  </si>
+  <si>
+    <t>Network fees buffer</t>
+  </si>
+  <si>
+    <t>Solana tx fee volatility w/ 7x safety margin</t>
+  </si>
+  <si>
+    <t>Current $118/mo x 12 x 7 safety</t>
+  </si>
+  <si>
+    <t>GO-TO-MARKET</t>
+  </si>
+  <si>
+    <t>Phase 1: Crypto-native seeding</t>
+  </si>
+  <si>
+    <t>Phase 2: Emerging markets expansion</t>
+  </si>
+  <si>
+    <t>Phase 3: Mainstream growth</t>
+  </si>
+  <si>
+    <t>Content marketing, crypto PR, partnership dev</t>
+  </si>
+  <si>
+    <t>CONTINGENCY BUFFER</t>
+  </si>
+  <si>
+    <t>Remainder to reach $500K seed round</t>
+  </si>
+  <si>
+    <t>TOTAL FUND</t>
+  </si>
+  <si>
     <t>Shareholder</t>
   </si>
   <si>
@@ -89,9 +602,6 @@
     <t>Product maturation, QA, operations. Identified critical bugs during MVP phase to ensure product readiness and representative of CEO when needed.</t>
   </si>
   <si>
-    <t>CTO (To Hire)</t>
-  </si>
-  <si>
     <t>Technical leadership, ensuring smart contract security, future AI integration plan, and investor relations.</t>
   </si>
   <si>
@@ -120,516 +630,6 @@
   </si>
   <si>
     <t>TOTAL</t>
-  </si>
-  <si>
-    <t>Year 1 Financial Summary</t>
-  </si>
-  <si>
-    <t>Profit &amp; Loss</t>
-  </si>
-  <si>
-    <t>Revenue</t>
-  </si>
-  <si>
-    <t>From Revenue sheet</t>
-  </si>
-  <si>
-    <t>Operating Expenses</t>
-  </si>
-  <si>
-    <t>From Opex sheet (post-funding)</t>
-  </si>
-  <si>
-    <t>Capital Expenses</t>
-  </si>
-  <si>
-    <t>From Capex sheet</t>
-  </si>
-  <si>
-    <t>Total Expenses</t>
-  </si>
-  <si>
-    <t>Profit</t>
-  </si>
-  <si>
-    <t>Profit Margin</t>
-  </si>
-  <si>
-    <t>GMV</t>
-  </si>
-  <si>
-    <t>Monthly GMV</t>
-  </si>
-  <si>
-    <t>Key Metrics</t>
-  </si>
-  <si>
-    <t>Monthly Burn (pre-funding)</t>
-  </si>
-  <si>
-    <t>Infrastructure only</t>
-  </si>
-  <si>
-    <t>Monthly Burn (post-funding)</t>
-  </si>
-  <si>
-    <t>Full team</t>
-  </si>
-  <si>
-    <t>Runway with $500K</t>
-  </si>
-  <si>
-    <t>Break-even</t>
-  </si>
-  <si>
-    <t>Month 1</t>
-  </si>
-  <si>
-    <t>Profitable from Day 1</t>
-  </si>
-  <si>
-    <t>Team Structure</t>
-  </si>
-  <si>
-    <t>Pre-Funding (3 founders)</t>
-  </si>
-  <si>
-    <t>Unpaid</t>
-  </si>
-  <si>
-    <t>Month 0 to funding</t>
-  </si>
-  <si>
-    <t>Post-Funding (6 people)</t>
-  </si>
-  <si>
-    <t>$69,749/month</t>
-  </si>
-  <si>
-    <t>$69,749/month - CEO, COO, CTO, Blockchain, Marketing, Content (incl. iOS fee)</t>
-  </si>
-  <si>
-    <t>Category</t>
-  </si>
-  <si>
-    <t>Base Users</t>
-  </si>
-  <si>
-    <t>Capture Rate</t>
-  </si>
-  <si>
-    <t>Active Users</t>
-  </si>
-  <si>
-    <t>Trx/Month per User</t>
-  </si>
-  <si>
-    <t>Total Trx/Month</t>
-  </si>
-  <si>
-    <t>Avg Trx Value ($)</t>
-  </si>
-  <si>
-    <t>Fee (%)</t>
-  </si>
-  <si>
-    <t>Fee per Trx ($)</t>
-  </si>
-  <si>
-    <t>Monthly Revenue ($)</t>
-  </si>
-  <si>
-    <t>Annual Revenue ($)</t>
-  </si>
-  <si>
-    <t>Reference</t>
-  </si>
-  <si>
-    <t>Monthly GMV ($)</t>
-  </si>
-  <si>
-    <t>Annual GMV ($)</t>
-  </si>
-  <si>
-    <t>Year 1 (1% Capture)</t>
-  </si>
-  <si>
-    <t>Tasks</t>
-  </si>
-  <si>
-    <t>Upwork 832K active clients × 1% capture × 0.2 trx/mo × $100 avg = $1.99M/yr GMV</t>
-  </si>
-  <si>
-    <t>Services</t>
-  </si>
-  <si>
-    <t>Goods</t>
-  </si>
-  <si>
-    <t>eBay 134M active buyers × 0.1% capture × 1.2 trx/mo × $50 avg = $96.48M/yr GMV</t>
-  </si>
-  <si>
-    <t>Secret Society</t>
-  </si>
-  <si>
-    <t>832 subs × $10/mo × 12mo = $99.8K/yr</t>
-  </si>
-  <si>
-    <t>Year 1 Total</t>
-  </si>
-  <si>
-    <t>Item</t>
-  </si>
-  <si>
-    <t>Cost per Unit ($)</t>
-  </si>
-  <si>
-    <t>Quantity</t>
-  </si>
-  <si>
-    <t>Unit</t>
-  </si>
-  <si>
-    <t>Frequency</t>
-  </si>
-  <si>
-    <t>Monthly Total ($)</t>
-  </si>
-  <si>
-    <t>Annual Total ($)</t>
-  </si>
-  <si>
-    <t>PRE-FUNDING (Month 0 to Funding)</t>
-  </si>
-  <si>
-    <t>Infrastructure</t>
-  </si>
-  <si>
-    <t>AWS ECR</t>
-  </si>
-  <si>
-    <t>User</t>
-  </si>
-  <si>
-    <t>Month</t>
-  </si>
-  <si>
-    <t>AWS pricing: $0.0035/user/mo</t>
-  </si>
-  <si>
-    <t>AWS DB</t>
-  </si>
-  <si>
-    <t>AWS pricing: $0.0015/user/mo</t>
-  </si>
-  <si>
-    <t>Blockchain</t>
-  </si>
-  <si>
-    <t>Network fee</t>
-  </si>
-  <si>
-    <t>Trx</t>
-  </si>
-  <si>
-    <t>Solana tx fee x 70 safety margin</t>
-  </si>
-  <si>
-    <t>Wallet fund</t>
-  </si>
-  <si>
-    <t>SOL for wallet operations</t>
-  </si>
-  <si>
-    <t>Pre-Funding Total</t>
-  </si>
-  <si>
-    <t>POST-FUNDING (Year 1)</t>
-  </si>
-  <si>
-    <t>Salary</t>
-  </si>
-  <si>
-    <t>CEO (Ghiffary)</t>
-  </si>
-  <si>
-    <t>Person</t>
-  </si>
-  <si>
-    <t>Founder salary</t>
-  </si>
-  <si>
-    <t>COO (Linh)</t>
-  </si>
-  <si>
-    <t>Operations + QA</t>
-  </si>
-  <si>
-    <t>Technical leadership</t>
-  </si>
-  <si>
-    <t>Lead Blockchain (Renard)</t>
-  </si>
-  <si>
-    <t>Smart contract + AWS</t>
-  </si>
-  <si>
-    <t>Senior Marketing Lead</t>
-  </si>
-  <si>
-    <t>Brand + Growth combined</t>
-  </si>
-  <si>
-    <t>Freelance Content Creator</t>
-  </si>
-  <si>
-    <t>Under Marketing Lead control</t>
-  </si>
-  <si>
-    <t>Office</t>
-  </si>
-  <si>
-    <t>Contact person</t>
-  </si>
-  <si>
-    <t>Company</t>
-  </si>
-  <si>
-    <t>Estonia e-residency</t>
-  </si>
-  <si>
-    <t>Rent exemption</t>
-  </si>
-  <si>
-    <t>Solana rent per account</t>
-  </si>
-  <si>
-    <t>Product</t>
-  </si>
-  <si>
-    <t>iOS App Store fee</t>
-  </si>
-  <si>
-    <t>Year</t>
-  </si>
-  <si>
-    <t>Annual</t>
-  </si>
-  <si>
-    <t>Apple Developer Program (business account)</t>
-  </si>
-  <si>
-    <t>Post-Funding Total</t>
-  </si>
-  <si>
-    <t>Total ($)</t>
-  </si>
-  <si>
-    <t>E-residency</t>
-  </si>
-  <si>
-    <t>Estonia e-residency program</t>
-  </si>
-  <si>
-    <t>Company registration</t>
-  </si>
-  <si>
-    <t>Estonia business registration</t>
-  </si>
-  <si>
-    <t>Wallet</t>
-  </si>
-  <si>
-    <t>Tangem Wallets (3 cards)</t>
-  </si>
-  <si>
-    <t>Bundle</t>
-  </si>
-  <si>
-    <t>Tangem official pricing</t>
-  </si>
-  <si>
-    <t>Trezor Safe 3</t>
-  </si>
-  <si>
-    <t>Trezor official pricing</t>
-  </si>
-  <si>
-    <t>Mainnet deployment</t>
-  </si>
-  <si>
-    <t>Solana program deployment cost</t>
-  </si>
-  <si>
-    <t>Security audit</t>
-  </si>
-  <si>
-    <t>Solana/Anchor audit market rate</t>
-  </si>
-  <si>
-    <t>Total Capex</t>
-  </si>
-  <si>
-    <t>Phase</t>
-  </si>
-  <si>
-    <t>Timeline</t>
-  </si>
-  <si>
-    <t>Target Audience</t>
-  </si>
-  <si>
-    <t>Channels</t>
-  </si>
-  <si>
-    <t>DAU Target</t>
-  </si>
-  <si>
-    <t>GMV Target ($)</t>
-  </si>
-  <si>
-    <t>CAC Budget ($)</t>
-  </si>
-  <si>
-    <t>Users Target</t>
-  </si>
-  <si>
-    <t>CAC per User ($)</t>
-  </si>
-  <si>
-    <t>Phase 1: Proof of Concept</t>
-  </si>
-  <si>
-    <t>Months 1-3</t>
-  </si>
-  <si>
-    <t>Crypto-native</t>
-  </si>
-  <si>
-    <t>Solana ecosystem, Galxe quests, GitHub bounties</t>
-  </si>
-  <si>
-    <t>$6K seed campaign budget. Marketing salaries in runway.</t>
-  </si>
-  <si>
-    <t>Solana devs, designers, auditors</t>
-  </si>
-  <si>
-    <t>Phase 2: Regional Expansion</t>
-  </si>
-  <si>
-    <t>Months 4-9</t>
-  </si>
-  <si>
-    <t>Emerging markets</t>
-  </si>
-  <si>
-    <t>USDC referral rewards, Superteam collabs, translation</t>
-  </si>
-  <si>
-    <t>$12K seed campaign budget. $17.5K/mo team in runway.</t>
-  </si>
-  <si>
-    <t>1.4B unbanked workers in SEA, LATAM, Africa</t>
-  </si>
-  <si>
-    <t>Phase 3: Mainstream</t>
-  </si>
-  <si>
-    <t>Months 10+</t>
-  </si>
-  <si>
-    <t>Mainstream</t>
-  </si>
-  <si>
-    <t>Content marketing, crypto PR, organic marketplace velocity</t>
-  </si>
-  <si>
-    <t>$7K seed campaign. $100M GMV driven by organic + fee advantage.</t>
-  </si>
-  <si>
-    <t>Fee-fatigued professionals + eBay goods sellers</t>
-  </si>
-  <si>
-    <t>YEAR 1 TOTAL</t>
-  </si>
-  <si>
-    <t>GTM campaign budgets only; $105K marketing team in Opex runway</t>
-  </si>
-  <si>
-    <t>Budget ($)</t>
-  </si>
-  <si>
-    <t>Breakdown</t>
-  </si>
-  <si>
-    <t>OPERATIONAL RUNWAY (6 months)</t>
-  </si>
-  <si>
-    <t>6 months post-funding Opex</t>
-  </si>
-  <si>
-    <t>ONE-TIME SETUP</t>
-  </si>
-  <si>
-    <t>Capex (from Capex sheet)</t>
-  </si>
-  <si>
-    <t>E-residency, wallets, mainnet, security audit</t>
-  </si>
-  <si>
-    <t>INFRASTRUCTURE SCALING</t>
-  </si>
-  <si>
-    <t>AWS scaling buffer</t>
-  </si>
-  <si>
-    <t>Scale 8K to 50K users w/ 6x safety margin</t>
-  </si>
-  <si>
-    <t>Target $250/mo − Current $42/mo x 12mo x 6</t>
-  </si>
-  <si>
-    <t>Network fees buffer</t>
-  </si>
-  <si>
-    <t>Solana tx fee volatility w/ 7x safety margin</t>
-  </si>
-  <si>
-    <t>Current $118/mo x 12 x 7 safety</t>
-  </si>
-  <si>
-    <t>GO-TO-MARKET</t>
-  </si>
-  <si>
-    <t>Phase 1: Crypto-native seeding</t>
-  </si>
-  <si>
-    <t>Phase 2: Emerging markets expansion</t>
-  </si>
-  <si>
-    <t>Phase 3: Mainstream growth</t>
-  </si>
-  <si>
-    <t>Content marketing, crypto PR, partnership dev</t>
-  </si>
-  <si>
-    <t>CONTINGENCY BUFFER</t>
-  </si>
-  <si>
-    <t>Remainder to reach $500K seed round</t>
-  </si>
-  <si>
-    <t>TOTAL FUND</t>
-  </si>
-  <si>
-    <t>Annual GMV = Total Trx x Avg Value x 12mo</t>
-  </si>
-  <si>
-    <t>Monthly GMV = Total Trx x Avg Value</t>
-  </si>
-  <si>
-    <t>$500K / monthly burn</t>
   </si>
 </sst>
 </file>
@@ -1048,7 +1048,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -1058,53 +1058,53 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="B4" s="3">
         <f>Revenue!K7</f>
         <v>1164480</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="B5" s="3">
         <f>Opex!H23</f>
         <v>836992.39520000003</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="B6" s="3">
         <f>Capex!F8</f>
         <v>20887.04</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="B7" s="3">
         <f>B5+B6</f>
@@ -1113,7 +1113,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="B8" s="5">
         <f>B4-B7</f>
@@ -1122,7 +1122,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="B9" s="6">
         <f>B8/B4</f>
@@ -1131,109 +1131,109 @@
     </row>
     <row r="11" spans="1:3" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="B11" s="3">
         <f>Revenue!N7</f>
         <v>100573440</v>
       </c>
       <c r="C11" t="s">
-        <v>194</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="B12" s="3">
         <f>Revenue!M7</f>
         <v>8381120</v>
       </c>
       <c r="C12" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="14" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>41</v>
-      </c>
-      <c r="B14" s="3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B13" s="3"/>
+    </row>
+    <row r="14" spans="1:3" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="3">
         <f>Opex!G7</f>
         <v>719.28960000000006</v>
       </c>
-      <c r="C14" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>43</v>
-      </c>
-      <c r="B15" s="3">
+      <c r="C15" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="3">
         <f>B5/12</f>
         <v>69749.366266666664</v>
       </c>
-      <c r="C15" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>45</v>
-      </c>
-      <c r="B16" s="7" t="e">
-        <f>500000/B13</f>
-        <v>#DIV/0!</v>
-      </c>
       <c r="C16" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>46</v>
-      </c>
-      <c r="B17" t="s">
-        <v>47</v>
+        <v>20</v>
+      </c>
+      <c r="B17" s="7">
+        <f>500000/B16</f>
+        <v>7.1685239130115344</v>
       </c>
       <c r="C17" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A19" s="14" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>50</v>
-      </c>
-      <c r="B20" t="s">
-        <v>51</v>
-      </c>
-      <c r="C20" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="18.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="14" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="B21" t="s">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="C21" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B22" s="3"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="18.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B23" s="3"/>
@@ -1242,20 +1242,20 @@
       <c r="B24" s="3"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A25" s="13"/>
-      <c r="B25" s="16"/>
+      <c r="B25" s="3"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B26" s="6"/>
+      <c r="A26" s="13"/>
+      <c r="B26" s="16"/>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B27" s="3"/>
-    </row>
-    <row r="29" spans="1:3" ht="18.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A29" s="1"/>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B30" s="3"/>
+      <c r="B27" s="6"/>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B28" s="3"/>
+    </row>
+    <row r="30" spans="1:3" ht="18.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="1"/>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B31" s="3"/>
@@ -1264,14 +1264,17 @@
       <c r="B32" s="3"/>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A33" s="13"/>
-      <c r="B33" s="16"/>
+      <c r="B33" s="3"/>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B34" s="6"/>
+      <c r="A34" s="13"/>
+      <c r="B34" s="16"/>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B35" s="3"/>
+      <c r="B35" s="6"/>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B36" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1299,56 +1302,56 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>69</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="B3">
         <v>832000</v>
@@ -1386,7 +1389,7 @@
         <v>49920</v>
       </c>
       <c r="L3" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="M3" s="3">
         <f>F3*G3</f>
@@ -1399,7 +1402,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="B4">
         <v>832000</v>
@@ -1437,7 +1440,7 @@
         <v>49920</v>
       </c>
       <c r="L4" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="M4" s="3">
         <f>F4*G4</f>
@@ -1450,7 +1453,7 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="B5">
         <v>134000000</v>
@@ -1488,7 +1491,7 @@
         <v>964800</v>
       </c>
       <c r="L5" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="M5" s="3">
         <f>F5*G5</f>
@@ -1501,7 +1504,7 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="B6">
         <v>832</v>
@@ -1539,7 +1542,7 @@
         <v>99840</v>
       </c>
       <c r="L6" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="M6" s="3">
         <f>F6*G6</f>
@@ -1552,7 +1555,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
-        <v>78</v>
+        <v>54</v>
       </c>
       <c r="C7" s="6"/>
       <c r="D7" s="9"/>
@@ -1698,44 +1701,44 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>80</v>
-      </c>
       <c r="D1" s="8" t="s">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>67</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="11" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="B3" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="C3" s="12">
         <v>3.5000000000000001E-3</v>
@@ -1744,10 +1747,10 @@
         <v>8320</v>
       </c>
       <c r="E3" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="F3" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="G3" s="3">
         <f>C3*D3</f>
@@ -1758,12 +1761,12 @@
         <v>349.44</v>
       </c>
       <c r="I3" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="C4" s="12">
         <v>1.5E-3</v>
@@ -1772,10 +1775,10 @@
         <v>8320</v>
       </c>
       <c r="E4" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="F4" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="G4" s="3">
         <f>C4*D4</f>
@@ -1786,15 +1789,15 @@
         <v>149.76</v>
       </c>
       <c r="I4" t="s">
-        <v>93</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="B5" t="s">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="C5" s="12">
         <v>6.9999999999999999E-4</v>
@@ -1803,10 +1806,10 @@
         <v>168128</v>
       </c>
       <c r="E5" t="s">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="F5" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="G5" s="3">
         <f>C5*D5</f>
@@ -1817,12 +1820,12 @@
         <v>1412.2752</v>
       </c>
       <c r="I5" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="C6" s="12">
         <v>0.14000000000000001</v>
@@ -1831,10 +1834,10 @@
         <v>4000</v>
       </c>
       <c r="E6" t="s">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="F6" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="G6" s="3">
         <f>C6*D6</f>
@@ -1845,12 +1848,12 @@
         <v>6720</v>
       </c>
       <c r="I6" t="s">
-        <v>99</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="C7" s="12"/>
       <c r="D7" s="9"/>
@@ -1871,7 +1874,7 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" s="11" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="C9" s="12"/>
       <c r="D9" s="9"/>
@@ -1880,10 +1883,10 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="B10" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="C10" s="12">
         <v>3.5000000000000001E-3</v>
@@ -1892,10 +1895,10 @@
         <v>8320</v>
       </c>
       <c r="E10" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="F10" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="G10" s="3">
         <f t="shared" ref="G10:G21" si="0">C10*D10</f>
@@ -1908,7 +1911,7 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="C11" s="12">
         <v>1.5E-3</v>
@@ -1917,10 +1920,10 @@
         <v>8320</v>
       </c>
       <c r="E11" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="F11" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="G11" s="3">
         <f t="shared" si="0"/>
@@ -1933,10 +1936,10 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="B12" t="s">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="C12" s="12">
         <v>6.9999999999999999E-4</v>
@@ -1945,10 +1948,10 @@
         <v>168128</v>
       </c>
       <c r="E12" t="s">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="F12" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="G12" s="3">
         <f t="shared" si="0"/>
@@ -1961,7 +1964,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="C13" s="12">
         <v>0.14000000000000001</v>
@@ -1970,10 +1973,10 @@
         <v>4000</v>
       </c>
       <c r="E13" t="s">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="F13" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="G13" s="3">
         <f t="shared" si="0"/>
@@ -1986,10 +1989,10 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="B14" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="C14" s="12">
         <v>12500</v>
@@ -1998,10 +2001,10 @@
         <v>1</v>
       </c>
       <c r="E14" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="F14" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="G14" s="3">
         <f t="shared" si="0"/>
@@ -2012,12 +2015,12 @@
         <v>150000</v>
       </c>
       <c r="I14" t="s">
-        <v>105</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="C15" s="12">
         <v>12000</v>
@@ -2026,10 +2029,10 @@
         <v>1</v>
       </c>
       <c r="E15" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="F15" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="G15" s="3">
         <f t="shared" si="0"/>
@@ -2040,12 +2043,12 @@
         <v>144000</v>
       </c>
       <c r="I15" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
-        <v>16</v>
+        <v>84</v>
       </c>
       <c r="C16" s="12">
         <v>15000</v>
@@ -2054,10 +2057,10 @@
         <v>1</v>
       </c>
       <c r="E16" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="F16" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="G16" s="3">
         <f t="shared" si="0"/>
@@ -2068,12 +2071,12 @@
         <v>180000</v>
       </c>
       <c r="I16" t="s">
-        <v>108</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="C17" s="12">
         <v>10000</v>
@@ -2082,10 +2085,10 @@
         <v>1</v>
       </c>
       <c r="E17" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="F17" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="G17" s="3">
         <f t="shared" si="0"/>
@@ -2096,12 +2099,12 @@
         <v>120000</v>
       </c>
       <c r="I17" t="s">
-        <v>110</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
-        <v>111</v>
+        <v>88</v>
       </c>
       <c r="C18" s="12">
         <v>15000</v>
@@ -2110,10 +2113,10 @@
         <v>1</v>
       </c>
       <c r="E18" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="F18" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="G18" s="3">
         <f t="shared" si="0"/>
@@ -2124,12 +2127,12 @@
         <v>180000</v>
       </c>
       <c r="I18" t="s">
-        <v>112</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B19" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="C19" s="12">
         <v>2500</v>
@@ -2138,10 +2141,10 @@
         <v>1</v>
       </c>
       <c r="E19" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="F19" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="G19" s="3">
         <f t="shared" si="0"/>
@@ -2152,15 +2155,15 @@
         <v>30000</v>
       </c>
       <c r="I19" t="s">
-        <v>114</v>
+        <v>91</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>115</v>
+        <v>92</v>
       </c>
       <c r="B20" t="s">
-        <v>116</v>
+        <v>93</v>
       </c>
       <c r="C20" s="12">
         <v>25</v>
@@ -2169,10 +2172,10 @@
         <v>1</v>
       </c>
       <c r="E20" t="s">
-        <v>117</v>
+        <v>94</v>
       </c>
       <c r="F20" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="G20" s="3">
         <f t="shared" si="0"/>
@@ -2183,12 +2186,12 @@
         <v>300</v>
       </c>
       <c r="I20" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="C21" s="12">
         <v>0.23799999999999999</v>
@@ -2197,10 +2200,10 @@
         <v>8320</v>
       </c>
       <c r="E21" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="F21" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="G21" s="3">
         <f t="shared" si="0"/>
@@ -2211,15 +2214,15 @@
         <v>23761.919999999998</v>
       </c>
       <c r="I21" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="B22" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="C22" s="12">
         <v>299</v>
@@ -2228,10 +2231,10 @@
         <v>1</v>
       </c>
       <c r="E22" t="s">
-        <v>123</v>
+        <v>100</v>
       </c>
       <c r="F22" t="s">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="G22" s="3">
         <f>C22*D22/12</f>
@@ -2242,12 +2245,12 @@
         <v>299</v>
       </c>
       <c r="I22" t="s">
-        <v>125</v>
+        <v>102</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" s="13" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="9"/>
@@ -2441,33 +2444,33 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>80</v>
-      </c>
       <c r="D1" s="8" t="s">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>127</v>
+        <v>104</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>67</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>115</v>
+        <v>92</v>
       </c>
       <c r="B2" t="s">
-        <v>128</v>
+        <v>105</v>
       </c>
       <c r="C2" s="10">
         <v>150</v>
@@ -2476,19 +2479,19 @@
         <v>2</v>
       </c>
       <c r="E2" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="F2" s="3">
         <f t="shared" ref="F2:F7" si="0">C2*D2</f>
         <v>300</v>
       </c>
       <c r="G2" t="s">
-        <v>129</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
       <c r="C3" s="10">
         <v>265</v>
@@ -2497,22 +2500,22 @@
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>117</v>
+        <v>94</v>
       </c>
       <c r="F3" s="3">
         <f t="shared" si="0"/>
         <v>265</v>
       </c>
       <c r="G3" t="s">
-        <v>131</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="B4" t="s">
-        <v>133</v>
+        <v>110</v>
       </c>
       <c r="C4" s="10">
         <v>81.36</v>
@@ -2521,19 +2524,19 @@
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="F4" s="3">
         <f t="shared" si="0"/>
         <v>81.36</v>
       </c>
       <c r="G4" t="s">
-        <v>135</v>
+        <v>112</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="C5" s="10">
         <v>68.680000000000007</v>
@@ -2542,22 +2545,22 @@
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="F5" s="3">
         <f t="shared" si="0"/>
         <v>68.680000000000007</v>
       </c>
       <c r="G5" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="B6" t="s">
-        <v>138</v>
+        <v>115</v>
       </c>
       <c r="C6" s="10">
         <v>172</v>
@@ -2566,19 +2569,19 @@
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="F6" s="3">
         <f t="shared" si="0"/>
         <v>172</v>
       </c>
       <c r="G6" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
-        <v>140</v>
+        <v>117</v>
       </c>
       <c r="C7" s="10">
         <v>20000</v>
@@ -2587,19 +2590,19 @@
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="F7" s="3">
         <f t="shared" si="0"/>
         <v>20000</v>
       </c>
       <c r="G7" t="s">
-        <v>141</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="C8" s="10"/>
       <c r="D8" s="9"/>
@@ -2631,48 +2634,48 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>144</v>
+        <v>121</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>145</v>
+        <v>122</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>146</v>
+        <v>123</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>147</v>
+        <v>124</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>149</v>
+        <v>126</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>150</v>
+        <v>127</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>151</v>
+        <v>128</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>67</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
-        <v>152</v>
+        <v>129</v>
       </c>
       <c r="B2" t="s">
-        <v>153</v>
+        <v>130</v>
       </c>
       <c r="C2" t="s">
-        <v>154</v>
+        <v>131</v>
       </c>
       <c r="D2" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="E2" s="9">
         <v>100</v>
@@ -2691,12 +2694,12 @@
         <v>60</v>
       </c>
       <c r="J2" t="s">
-        <v>156</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C3" t="s">
-        <v>157</v>
+        <v>134</v>
       </c>
       <c r="E3" s="9"/>
       <c r="F3" s="3"/>
@@ -2713,16 +2716,16 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
-        <v>158</v>
+        <v>135</v>
       </c>
       <c r="B5" t="s">
-        <v>159</v>
+        <v>136</v>
       </c>
       <c r="C5" t="s">
-        <v>160</v>
+        <v>137</v>
       </c>
       <c r="D5" t="s">
-        <v>161</v>
+        <v>138</v>
       </c>
       <c r="E5" s="9">
         <v>5000</v>
@@ -2741,12 +2744,12 @@
         <v>2.4</v>
       </c>
       <c r="J5" t="s">
-        <v>162</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C6" t="s">
-        <v>163</v>
+        <v>140</v>
       </c>
       <c r="E6" s="9"/>
       <c r="F6" s="3"/>
@@ -2763,16 +2766,16 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
-        <v>164</v>
+        <v>141</v>
       </c>
       <c r="B8" t="s">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="C8" t="s">
-        <v>166</v>
+        <v>143</v>
       </c>
       <c r="D8" t="s">
-        <v>167</v>
+        <v>144</v>
       </c>
       <c r="E8" s="9">
         <v>50000</v>
@@ -2791,12 +2794,12 @@
         <v>0.84134615384615385</v>
       </c>
       <c r="J8" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C9" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="E9" s="9"/>
       <c r="F9" s="3"/>
@@ -2813,7 +2816,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" s="11" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
       <c r="E11" s="9"/>
       <c r="F11" s="3"/>
@@ -2829,7 +2832,7 @@
         <v>3.0048076923076925</v>
       </c>
       <c r="J11" t="s">
-        <v>171</v>
+        <v>148</v>
       </c>
     </row>
   </sheetData>
@@ -2850,31 +2853,31 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="15" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>67</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="17" t="s">
-        <v>174</v>
+        <v>151</v>
       </c>
       <c r="C2" s="3">
         <f>Opex!G23*6</f>
         <v>418496.19760000007</v>
       </c>
       <c r="D2" t="s">
-        <v>175</v>
+        <v>152</v>
       </c>
       <c r="E2">
         <f>Opex!G23*6</f>
@@ -2886,7 +2889,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="17" t="s">
-        <v>176</v>
+        <v>153</v>
       </c>
       <c r="C4" s="3">
         <f>C5</f>
@@ -2895,14 +2898,14 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
-        <v>177</v>
+        <v>154</v>
       </c>
       <c r="C5" s="3">
         <f>Capex!F8</f>
         <v>20887.04</v>
       </c>
       <c r="D5" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="E5">
         <f>Capex!F8</f>
@@ -2914,7 +2917,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>179</v>
+        <v>156</v>
       </c>
       <c r="C7" s="3">
         <f>C8+C9</f>
@@ -2924,32 +2927,32 @@
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="13"/>
       <c r="B8" t="s">
-        <v>180</v>
+        <v>157</v>
       </c>
       <c r="C8" s="3">
         <f>((0.0035+0.0015)*50000-(Opex!G10+Opex!G11))*12*6</f>
         <v>15004.800000000001</v>
       </c>
       <c r="D8" t="s">
-        <v>181</v>
+        <v>158</v>
       </c>
       <c r="E8" t="s">
-        <v>182</v>
+        <v>159</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
-        <v>183</v>
+        <v>160</v>
       </c>
       <c r="C9" s="3">
         <f>Opex!G12*12*7</f>
         <v>9885.9264000000003</v>
       </c>
       <c r="D9" t="s">
-        <v>184</v>
+        <v>161</v>
       </c>
       <c r="E9" t="s">
-        <v>185</v>
+        <v>162</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
@@ -2957,7 +2960,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>186</v>
+        <v>163</v>
       </c>
       <c r="C11" s="3">
         <f>C12+C13+C14</f>
@@ -2967,48 +2970,48 @@
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="13"/>
       <c r="B12" t="s">
-        <v>187</v>
+        <v>164</v>
       </c>
       <c r="C12" s="3">
         <f>'Go-to-Market'!G2</f>
         <v>6000</v>
       </c>
       <c r="D12" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="E12" t="s">
-        <v>153</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="4"/>
       <c r="B13" t="s">
-        <v>188</v>
+        <v>165</v>
       </c>
       <c r="C13" s="3">
         <f>'Go-to-Market'!G5</f>
         <v>12000</v>
       </c>
       <c r="D13" t="s">
-        <v>161</v>
+        <v>138</v>
       </c>
       <c r="E13" t="s">
-        <v>159</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
       <c r="C14" s="3">
         <f>'Go-to-Market'!G8</f>
         <v>7000</v>
       </c>
       <c r="D14" t="s">
-        <v>190</v>
+        <v>167</v>
       </c>
       <c r="E14" t="s">
-        <v>165</v>
+        <v>142</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
@@ -3017,14 +3020,14 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>191</v>
+        <v>168</v>
       </c>
       <c r="C16" s="3">
         <f>500000-C2-C4-C7-C11</f>
         <v>10726.035999999927</v>
       </c>
       <c r="D16" t="s">
-        <v>192</v>
+        <v>169</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
@@ -3032,7 +3035,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="13" t="s">
-        <v>193</v>
+        <v>170</v>
       </c>
       <c r="C18" s="3">
         <f>C2+C4+C7+C11+C16</f>
@@ -3077,30 +3080,30 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
-        <v>0</v>
+        <v>171</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1</v>
+        <v>172</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>2</v>
+        <v>173</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>3</v>
+        <v>174</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>4</v>
+        <v>175</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>5</v>
+        <v>176</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>177</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>178</v>
       </c>
       <c r="C2" s="6">
         <v>0.6</v>
@@ -3109,18 +3112,18 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>179</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>180</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>181</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>182</v>
       </c>
       <c r="C3" s="6">
         <v>0.1</v>
@@ -3129,18 +3132,18 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>179</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>183</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>184</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>185</v>
       </c>
       <c r="C4" s="6">
         <v>0.1</v>
@@ -3149,15 +3152,15 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>179</v>
       </c>
       <c r="F4" t="s">
-        <v>15</v>
+        <v>186</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
-        <v>16</v>
+        <v>84</v>
       </c>
       <c r="C5" s="6">
         <v>0.15</v>
@@ -3166,18 +3169,18 @@
         <v>0.1</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>179</v>
       </c>
       <c r="F5" t="s">
-        <v>17</v>
+        <v>187</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>188</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>189</v>
       </c>
       <c r="C6" s="6">
         <v>0.05</v>
@@ -3186,18 +3189,18 @@
         <v>0.05</v>
       </c>
       <c r="E6" t="s">
-        <v>20</v>
+        <v>190</v>
       </c>
       <c r="F6" t="s">
-        <v>21</v>
+        <v>191</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>192</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>193</v>
       </c>
       <c r="C7" s="6">
         <v>0</v>
@@ -3206,15 +3209,15 @@
         <v>0.15</v>
       </c>
       <c r="E7" t="s">
-        <v>24</v>
+        <v>194</v>
       </c>
       <c r="F7" t="s">
-        <v>25</v>
+        <v>195</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
-        <v>26</v>
+        <v>196</v>
       </c>
       <c r="C8" s="6">
         <f>SUM(C2:C7)</f>
